--- a/resources/templates/standard/M1200-01.xlsx
+++ b/resources/templates/standard/M1200-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>호기</t>
   </si>
@@ -839,7 +842,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -955,34 +960,34 @@
     </row>
     <row r="6" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -997,24 +1002,24 @@
     <row r="7" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1031,7 +1036,7 @@
     </row>
     <row r="8" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -1171,7 +1176,7 @@
     </row>
     <row r="14" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1311,7 +1316,7 @@
     </row>
     <row r="20" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -1428,7 +1433,7 @@
     </row>
     <row r="25" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1744,22 +1749,22 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R38" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S38" s="30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T38" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U38" s="30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" ht="15.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
